--- a/excel/pacifico-ayacucho_capacitaciones.xlsx
+++ b/excel/pacifico-ayacucho_capacitaciones.xlsx
@@ -966,12 +966,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C004182546</t>
+          <t>C004237270</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C004182546 - PRADO ROCA EDITH</t>
+          <t>C004237270 - VARGAS SAUÑE JHEAN CARLOS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C004186439</t>
+          <t>C004182546</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C004186439 - FLORES ALBITES JUANA</t>
+          <t>C004182546 - PRADO ROCA EDITH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C004189005</t>
+          <t>C004186439</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
+          <t>C004186439 - FLORES ALBITES JUANA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1200,19 +1200,23 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1248,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C004189006</t>
+          <t>C004189005</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C004189006 - GAMBOA ENCISO ELIANA</t>
+          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1334,12 +1338,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C004189011</t>
+          <t>C004189006</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C004189011 - SAUNE YUPANQUI MAURA NIEVES</t>
+          <t>C004189006 - GAMBOA ENCISO ELIANA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1380,7 +1384,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1424,12 +1428,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004237270</t>
+          <t>C004189011</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004237270 - VARGAS SAUÑE JHEAN CARLOS</t>
+          <t>C004189011 - SAUNE YUPANQUI MAURA NIEVES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1470,23 +1474,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001640679</t>
+          <t>C001668200</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001640679 - YUPANQUI QUISPE LOURDES</t>
+          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001687768</t>
+          <t>C001669740</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
+          <t>C001669740 - JANAMPA GALINDO FLORA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001668200</t>
+          <t>C001640679</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
+          <t>C001640679 - YUPANQUI QUISPE LOURDES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001669740</t>
+          <t>C001687768</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001669740 - JANAMPA GALINDO FLORA</t>
+          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001219345</t>
+          <t>C001217185</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001219345 - ALVITEZ TACO IRMA</t>
+          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001217185</t>
+          <t>C001219345</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
+          <t>C001219345 - ALVITEZ TACO IRMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001198370</t>
+          <t>C001447727</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001198370 - GUTIERREZ CERDA NORY</t>
+          <t>C001447727 - QUISPE CARRASCO MARGOT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2502,13 +2502,17 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2544,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004185791</t>
+          <t>C004187315</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C004185791 - ZANABRIA DURAND ROSA</t>
+          <t>C004187315 - ESPINO YARANGA HONORIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2634,12 +2638,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004187301</t>
+          <t>C001751679</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C004187301 - MENDEZ HUAMAN YANINA</t>
+          <t>C001751679 - BEDRIÑANA MONTES CELIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2686,13 +2690,17 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2732,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004187315</t>
+          <t>C001724460</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C004187315 - ESPINO YARANGA HONORIA</t>
+          <t>C001724460 - TINCO MENDOZA ANA KARINA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2818,12 +2826,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C001751679</t>
+          <t>C001475324</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C001751679 - BEDRIÑANA MONTES CELIA</t>
+          <t>C001475324 - RICHARTE CEBRIAN MARIA YSABEL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2864,23 +2872,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2916,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001724460</t>
+          <t>C001475217</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001724460 - TINCO MENDOZA ANA KARINA</t>
+          <t>C001475217 - CAMPOS COLOS AGUSTINA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2958,7 +2962,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3006,12 +3010,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001447727</t>
+          <t>C004185791</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001447727 - QUISPE CARRASCO MARGOT</t>
+          <t>C004185791 - ZANABRIA DURAND ROSA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3052,7 +3056,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3100,12 +3104,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001475324</t>
+          <t>C004168930</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001475324 - RICHARTE CEBRIAN MARIA YSABEL</t>
+          <t>C004168930 - GUTIERREZ PRADO ROSA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3146,19 +3150,23 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3198,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001475217</t>
+          <t>C004187301</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001475217 - CAMPOS COLOS AGUSTINA</t>
+          <t>C004187301 - MENDEZ HUAMAN YANINA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3236,23 +3244,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3288,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001725257</t>
+          <t>C000921432</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001725257 - SULCA CANCHO HAYDEE</t>
+          <t>C000921432 - PASTOR RUA BETTY LILIANA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3374,12 +3378,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001729117</t>
+          <t>C000922061</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001729117 - DE LA CRUZ FLORES ELSA ANTONIA</t>
+          <t>C000922061 - ROMERO RUIZ VILMA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3426,17 +3430,13 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001763844</t>
+          <t>C001381785</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001763844 - REVOLLAR HUAMAN ROQUE</t>
+          <t>C001381785 - MARTINEZ DE PARIONA VICTORIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3520,17 +3520,13 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3558,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004168930</t>
+          <t>C001198370</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C004168930 - GUTIERREZ PRADO ROSA</t>
+          <t>C001198370 - GUTIERREZ CERDA NORY</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3608,23 +3604,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3648,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C000921432</t>
+          <t>C001477308</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C000921432 - PASTOR RUA BETTY LILIANA</t>
+          <t>C001477308 - CAMPOS COLOS HAYDEE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3702,19 +3694,23 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3742,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C000922061</t>
+          <t>C001557392</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C000922061 - ROMERO RUIZ VILMA</t>
+          <t>C001557392 - FLORES TAYPE JOHANA LISSET</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3836,12 +3832,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001477308</t>
+          <t>C001564006</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001477308 - CAMPOS COLOS HAYDEE</t>
+          <t>C001564006 - BELLIDO BAUTISTA EDMUNDO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3930,12 +3926,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001381785</t>
+          <t>C001640455</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001381785 - MARTINEZ DE PARIONA VICTORIA</t>
+          <t>C001640455 - TAYPE ÑUFLO NERY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3976,19 +3972,23 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001557392</t>
+          <t>C001663749</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001557392 - FLORES TAYPE JOHANA LISSET</t>
+          <t>C001663749 - VEGA MENDOZA UBER ANTENOR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4066,19 +4066,23 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4110,12 +4114,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001564006</t>
+          <t>C001763844</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001564006 - BELLIDO BAUTISTA EDMUNDO</t>
+          <t>C001763844 - REVOLLAR HUAMAN ROQUE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4156,7 +4160,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4204,12 +4208,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001670779</t>
+          <t>C001729117</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
+          <t>C001729117 - DE LA CRUZ FLORES ELSA ANTONIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4250,7 +4254,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -4298,12 +4302,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001640455</t>
+          <t>C001725257</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001640455 - TAYPE ÑUFLO NERY</t>
+          <t>C001725257 - SULCA CANCHO HAYDEE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4350,17 +4354,13 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001663749</t>
+          <t>C001670779</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001663749 - VEGA MENDOZA UBER ANTENOR</t>
+          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001385573</t>
+          <t>C000920583</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001385573 - LLANTOY HUAMAN MARLENY YANET</t>
+          <t>C000920583 - CURI RIVEROS JUANA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4532,23 +4532,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4576,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001412859</t>
+          <t>C000920586</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001412859 - MALLMA LOZANO JUANA VICTORIA</t>
+          <t>C000920586 - QUISPE DE ARESTEGUI LIDIA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4674,12 +4670,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C000920583</t>
+          <t>C000920604</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C000920583 - CURI RIVEROS JUANA</t>
+          <t>C000920604 - QUISPE DE HUARANCCAY DONATILDA N.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4720,19 +4716,23 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C000920586</t>
+          <t>C000920651</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C000920586 - QUISPE DE ARESTEGUI LIDIA</t>
+          <t>C000920651 - ONCEBAY PARIONA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C000920604</t>
+          <t>C000921479</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C000920604 - QUISPE DE HUARANCCAY DONATILDA N.</t>
+          <t>C000921479 - CUYA PRADO GLADYS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C000920651</t>
+          <t>C000922381</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C000920651 - ONCEBAY PARIONA ALEJANDRINA</t>
+          <t>C000922381 - LOPEZ ALIAGA DE ARENAS MIRIAM YANINA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C000921479</t>
+          <t>C000922487</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C000921479 - CUYA PRADO GLADYS</t>
+          <t>C000922487 - PARADO QUISPE FLORABEL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C000922381</t>
+          <t>C001385573</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C000922381 - LOPEZ ALIAGA DE ARENAS MIRIAM YANINA</t>
+          <t>C001385573 - LLANTOY HUAMAN MARLENY YANET</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C000922487</t>
+          <t>C001115126</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C000922487 - PARADO QUISPE FLORABEL</t>
+          <t>C001115126 - MACHACA  SATURNINA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5280,23 +5280,19 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5324,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001115126</t>
+          <t>C001643213</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001115126 - MACHACA  SATURNINA</t>
+          <t>C001643213 - ARANGO FERNANDEZ GABRIELA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5418,12 +5414,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001711513</t>
+          <t>C001583705</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
+          <t>C001583705 - GUZMAN PALACIOS GLORIA BRIGITH</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5470,17 +5466,13 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5504,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001684339</t>
+          <t>C001617091</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001684339 - ROSALES ILLACCANQUI EDELMIRA SALOME</t>
+          <t>C001617091 - CAMPOS CURI SILVIA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5558,7 +5550,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -5606,12 +5598,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001643213</t>
+          <t>C001684339</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001643213 - ARANGO FERNANDEZ GABRIELA</t>
+          <t>C001684339 - ROSALES ILLACCANQUI EDELMIRA SALOME</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5658,13 +5650,17 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5786,12 +5782,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001583705</t>
+          <t>C001549867</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C001583705 - GUZMAN PALACIOS GLORIA BRIGITH</t>
+          <t>C001549867 - TAIPE LLANTO NOEMI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5832,19 +5828,23 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001617091</t>
+          <t>C001550439</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C001617091 - CAMPOS CURI SILVIA</t>
+          <t>C001550439 - TAIPE LLANTO NOEMI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5928,17 +5928,13 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5966,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001549867</t>
+          <t>C001533449</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001549867 - TAIPE LLANTO NOEMI</t>
+          <t>C001533449 - RODRIGUEZ LOPEZ GLORIA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6016,7 +6012,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -6064,12 +6060,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001550439</t>
+          <t>C001412859</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001550439 - TAIPE LLANTO NOEMI</t>
+          <t>C001412859 - MALLMA LOZANO JUANA VICTORIA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6110,19 +6106,23 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001533449</t>
+          <t>C004167919</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001533449 - RODRIGUEZ LOPEZ GLORIA</t>
+          <t>C004167919 - SICHA HACHA FELIPE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6206,17 +6206,13 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6248,12 +6244,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C004188382</t>
+          <t>C004181104</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C004188382 - ROMERO DE MENDOZA VICTORIA CELSA</t>
+          <t>C004181104 - IÑAUSI ARONI MARIVEL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6300,17 +6296,13 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6342,12 +6334,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C004167919</t>
+          <t>C004160956</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C004167919 - SICHA HACHA FELIPE</t>
+          <t>C004160956 - YAURI PARIONA EDITH</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6432,12 +6424,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C004185571</t>
+          <t>C004188382</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C004185571 - ASTO PALACIOS GIOVANNI ANDRE</t>
+          <t>C004188382 - ROMERO DE MENDOZA VICTORIA CELSA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6478,7 +6470,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6526,12 +6518,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C004181104</t>
+          <t>C004185571</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C004181104 - IÑAUSI ARONI MARIVEL</t>
+          <t>C004185571 - ASTO PALACIOS GIOVANNI ANDRE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6572,19 +6564,23 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6616,12 +6612,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C004160956</t>
+          <t>C001723407</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C004160956 - YAURI PARIONA EDITH</t>
+          <t>C001723407 - CONTRERAS ÑAÑACC-HUARI TANIA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6662,19 +6658,23 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001723407</t>
+          <t>C001711513</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001723407 - CONTRERAS ÑAÑACC-HUARI TANIA</t>
+          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -6890,12 +6890,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C000920444</t>
+          <t>C001216294</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C000920444 - QUISPE CONTRERAS RENEE</t>
+          <t>C001216294 - QUICHCA JAYO RUDECINDA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6942,17 +6942,13 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6984,12 +6980,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C000921537</t>
+          <t>C000920444</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C000921537 - ARANGO QUISPE EDITA</t>
+          <t>C000920444 - QUISPE CONTRERAS RENEE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7036,13 +7032,17 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001216294</t>
+          <t>C000921537</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001216294 - QUICHCA JAYO RUDECINDA</t>
+          <t>C000921537 - ARANGO QUISPE EDITA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001668427</t>
+          <t>C001538020</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001668427 - RAMIREZ MAÑUICO KARINA</t>
+          <t>C001538020 - YAURI QUISPE CIRILA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001631125</t>
+          <t>C001509217</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001631125 - ATAUQUI SULCA LUZMILA</t>
+          <t>C001509217 - ARANA PALOMINO BERTHA MAGDALENA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001632867</t>
+          <t>C001469477</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001632867 - CALLE QUISPE EDUARDO</t>
+          <t>C001469477 - GONZALEZ DE GOMEZ ROSA NETTA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
@@ -7536,12 +7536,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001623885</t>
+          <t>C001668427</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001623885 - PALOMINO RODRIGUEZ DARWIN ANSHELMO</t>
+          <t>C001668427 - RAMIREZ MAÑUICO KARINA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7582,19 +7582,23 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7630,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001509217</t>
+          <t>C001631125</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001509217 - ARANA PALOMINO BERTHA MAGDALENA</t>
+          <t>C001631125 - ATAUQUI SULCA LUZMILA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7672,7 +7676,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
@@ -7720,12 +7724,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001469477</t>
+          <t>C001632867</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001469477 - GONZALEZ DE GOMEZ ROSA NETTA</t>
+          <t>C001632867 - CALLE QUISPE EDUARDO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7761,12 +7765,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
@@ -7810,12 +7814,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001538020</t>
+          <t>C001623885</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C001538020 - YAURI QUISPE CIRILA</t>
+          <t>C001623885 - PALOMINO RODRIGUEZ DARWIN ANSHELMO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7862,17 +7866,13 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001728289</t>
+          <t>C001730724</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C001728289 - CRISOSTOMO DE QUISPE BERNARDINA</t>
+          <t>C001730724 - GOMEZ MEDINA OLGA MARLENY</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S86" t="inlineStr"/>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001730724</t>
+          <t>C001728289</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C001730724 - GOMEZ MEDINA OLGA MARLENY</t>
+          <t>C001728289 - CRISOSTOMO DE QUISPE BERNARDINA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S87" t="inlineStr"/>
@@ -8742,12 +8742,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C001403702</t>
+          <t>C001216296</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C001403702 - QUINTO BARRIOS GABRIELA</t>
+          <t>C001216296 - DE LA CRUZ VASQUEZ HILDA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8794,13 +8794,17 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8836,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C001418793</t>
+          <t>C001225337</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C001418793 - YANCCE RUIZ FIDENCIANA</t>
+          <t>C001225337 - VENTURA FLORES ZENOBIA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8884,17 +8888,13 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8926,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001216296</t>
+          <t>C001225339</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C001216296 - DE LA CRUZ VASQUEZ HILDA</t>
+          <t>C001225339 - MENESES YANCE HERLINDA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S92" t="inlineStr"/>
@@ -8983,12 +8983,12 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9020,12 +9020,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001225337</t>
+          <t>C001418793</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C001225337 - VENTURA FLORES ZENOBIA</t>
+          <t>C001418793 - YANCCE RUIZ FIDENCIANA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9072,13 +9072,17 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9110,12 +9114,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001225339</t>
+          <t>C001403702</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C001225339 - MENESES YANCE HERLINDA</t>
+          <t>C001403702 - QUINTO BARRIOS GABRIELA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9156,23 +9160,19 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001766607</t>
+          <t>C001696477</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C001766607 - CORDERO MARTINEZ OLINDA</t>
+          <t>C001696477 - MAURICIO HUAMAN BETSIBEL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S100" t="inlineStr"/>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001696477</t>
+          <t>C000920871</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C001696477 - MAURICIO HUAMAN BETSIBEL</t>
+          <t>C000920871 - FERNANDEZ MUNAYLLA CIPRIANA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S103" t="inlineStr"/>
@@ -10136,12 +10136,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C004101278</t>
+          <t>C001766607</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C004101278 - PRADO LEON MARIA MAGDALENA</t>
+          <t>C001766607 - CORDERO MARTINEZ OLINDA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C004184774</t>
+          <t>C004101278</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C004184774 - ESCALANTE HUAMAN FLORA</t>
+          <t>C004101278 - PRADO LEON MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C004182533</t>
+          <t>C004184774</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C004182533 - HUERTAS ARANGO LARRY</t>
+          <t>C004184774 - ESCALANTE HUAMAN FLORA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S107" t="inlineStr"/>
@@ -10381,12 +10381,12 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001730310</t>
+          <t>C004182533</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001730310 - PALOMINO PRADO EMELYN ESTEFANI</t>
+          <t>C004182533 - HUERTAS ARANGO LARRY</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10606,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C000920871</t>
+          <t>C001730310</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C000920871 - FERNANDEZ MUNAYLLA CIPRIANA</t>
+          <t>C001730310 - PALOMINO PRADO EMELYN ESTEFANI</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S110" t="inlineStr"/>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C004192068</t>
+          <t>C004186418</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C004192068 - CARRENO ALBURQUEQUE JUAN ISAIAS</t>
+          <t>C004186418 - CHOCCE CURI CLAIDE CRISTINA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10846,17 +10846,13 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10888,12 +10884,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C004186418</t>
+          <t>C004192068</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C004186418 - CHOCCE CURI CLAIDE CRISTINA</t>
+          <t>C004192068 - CARRENO ALBURQUEQUE JUAN ISAIAS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10940,13 +10936,17 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11166,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001672757</t>
+          <t>C001503289</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C001672757 - GUTIERREZ HUAYLLASCO CARLOS HONORATO</t>
+          <t>C001503289 - ALFARO GUTIERREZ FLORINA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S116" t="inlineStr"/>
@@ -11223,12 +11223,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001503289</t>
+          <t>C001672757</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C001503289 - ALFARO GUTIERREZ FLORINA</t>
+          <t>C001672757 - GUTIERREZ HUAYLLASCO CARLOS HONORATO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11902,12 +11902,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C004060033</t>
+          <t>C001563236</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C004060033 - LEON YANA ANGEL EDDU</t>
+          <t>C001563236 - TELLO CUADROS YENI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S124" t="inlineStr"/>
@@ -12180,12 +12180,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001750370</t>
+          <t>C001704643</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C001750370 - RISCO MENTANA MILAGROS SOFIA</t>
+          <t>C001704643 - HUAMANI DE CORDOVA PAULINA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S127" t="inlineStr"/>
@@ -12274,12 +12274,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001704643</t>
+          <t>C000921887</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C001704643 - HUAMANI DE CORDOVA PAULINA</t>
+          <t>C000921887 - MENDOZA AUQUI TRINIDAD</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001563236</t>
+          <t>C001405716</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C001563236 - TELLO CUADROS YENI</t>
+          <t>C001405716 - FERNANDEZ DE BAJALQUI CARMEN</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12420,13 +12420,17 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -12458,12 +12462,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001405716</t>
+          <t>C004060033</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>C001405716 - FERNANDEZ DE BAJALQUI CARMEN</t>
+          <t>C004060033 - LEON YANA ANGEL EDDU</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12504,23 +12508,19 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C000921887</t>
+          <t>C001750370</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C000921887 - MENDOZA AUQUI TRINIDAD</t>
+          <t>C001750370 - RISCO MENTANA MILAGROS SOFIA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
@@ -14408,12 +14408,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001709576</t>
+          <t>C001722581</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C001709576 - JAULIS PALOMINO JULIAN LUIS</t>
+          <t>C001722581 - HUYHUA CURO ILIANA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C001722581</t>
+          <t>C001709576</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C001722581 - HUYHUA CURO ILIANA</t>
+          <t>C001709576 - JAULIS PALOMINO JULIAN LUIS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C001728705</t>
+          <t>C001709575</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C001728705 - LOPEZ CARDENAS ROBERTH</t>
+          <t>C001709575 - VARGAS ORIUNDO CRISTHIAN</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
@@ -14841,12 +14841,12 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001761755</t>
+          <t>C001728705</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>C001761755 - HUALLPA PUCLLA LUZMERY</t>
+          <t>C001728705 - LOPEZ CARDENAS ROBERTH</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -15112,19 +15112,23 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15156,12 +15160,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C004100273</t>
+          <t>C001761755</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>C004100273 - ROCA TORRES GIANELLA MIGCELI</t>
+          <t>C001761755 - HUALLPA PUCLLA LUZMERY</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15202,23 +15206,19 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15250,12 +15250,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C004101499</t>
+          <t>C004100273</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>C004101499 - TINEO CCENHUA AMANDA</t>
+          <t>C004100273 - ROCA TORRES GIANELLA MIGCELI</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S160" t="inlineStr"/>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C004163224</t>
+          <t>C004101499</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C004163224 - HUAMAN CUETO KAHORY SIOMI NEYDA</t>
+          <t>C004101499 - TINEO CCENHUA AMANDA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
@@ -15438,12 +15438,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>C004168926</t>
+          <t>C004163224</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>C004168926 - HUAMAN CURO ABEL</t>
+          <t>C004163224 - HUAMAN CUETO KAHORY SIOMI NEYDA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S162" t="inlineStr"/>
@@ -15532,12 +15532,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001709575</t>
+          <t>C004168926</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C001709575 - VARGAS ORIUNDO CRISTHIAN</t>
+          <t>C004168926 - HUAMAN CURO ABEL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S163" t="inlineStr"/>
@@ -15589,12 +15589,12 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17118,12 +17118,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>C001326474</t>
+          <t>C001008076</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C001326474 - GUILLEN DE RAMIREZ REYNA MATILDE</t>
+          <t>C001008076 - MARTINEZ GAMBOA DELIA GLORIA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S180" t="inlineStr"/>
@@ -17212,12 +17212,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C001008076</t>
+          <t>C001016621</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C001008076 - MARTINEZ GAMBOA DELIA GLORIA</t>
+          <t>C001016621 - VEGA SULCA VICTOR ALFREDO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -17306,12 +17306,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C001016621</t>
+          <t>C001664645</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C001016621 - VEGA SULCA VICTOR ALFREDO</t>
+          <t>C001664645 - ESPINOZA MITMA JULIA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -17352,7 +17352,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S182" t="inlineStr"/>
@@ -17400,12 +17400,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001664645</t>
+          <t>C001326474</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001664645 - ESPINOZA MITMA JULIA</t>
+          <t>C001326474 - GUILLEN DE RAMIREZ REYNA MATILDE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S183" t="inlineStr"/>
@@ -19276,12 +19276,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C001544857</t>
+          <t>C001400639</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>C001544857 - MISARAYME TACURI HAYDEE</t>
+          <t>C001400639 - HUAMAN PACHECO ERNESTINA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S203" t="inlineStr"/>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19464,12 +19464,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>C001400639</t>
+          <t>C001544857</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>C001400639 - HUAMAN PACHECO ERNESTINA</t>
+          <t>C001544857 - MISARAYME TACURI HAYDEE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S205" t="inlineStr"/>
@@ -19521,12 +19521,12 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20212,12 +20212,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C001729759</t>
+          <t>C001721463</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C001729759 - GAMBOA CAYLLAHUA HAYDEE</t>
+          <t>C001721463 - JM INVBUSS E.I.R.L.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S213" t="inlineStr"/>
@@ -20306,12 +20306,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C001721463</t>
+          <t>C001648793</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C001721463 - JM INVBUSS E.I.R.L.</t>
+          <t>C001648793 - ALCANTARA VALLEJO ROSA ARACELI</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S214" t="inlineStr"/>
@@ -20400,12 +20400,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C001648793</t>
+          <t>C001729759</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C001648793 - ALCANTARA VALLEJO ROSA ARACELI</t>
+          <t>C001729759 - GAMBOA CAYLLAHUA HAYDEE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -20776,12 +20776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C004238153</t>
+          <t>C004203840</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>C004238153 - ROMANI PALOMINO MAXIMILIANA</t>
+          <t>C004203840 - CARDENAS PENA MALENA MARITZA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S219" t="inlineStr"/>
@@ -20833,12 +20833,12 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -20870,12 +20870,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C004203840</t>
+          <t>C004238153</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>C004203840 - CARDENAS PENA MALENA MARITZA</t>
+          <t>C004238153 - ROMANI PALOMINO MAXIMILIANA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S220" t="inlineStr"/>
@@ -20927,12 +20927,12 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20964,12 +20964,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001216332</t>
+          <t>C000920369</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001216332 - GARCIA GARCIA DE ORE LAURA</t>
+          <t>C000920369 - DEZA SANDOVAL FRIDA MARILU</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -21000,7 +21000,7 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S221" t="inlineStr"/>
@@ -21058,12 +21058,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001336201</t>
+          <t>C000921710</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C001336201 - CURI VALENCIA ANTONIA</t>
+          <t>C000921710 - PAREDES ROCA DARIO OCTAVIO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -21115,12 +21115,12 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21152,12 +21152,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001141675</t>
+          <t>C000921884</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C001141675 - RIVEROS BELLIDO JULIA</t>
+          <t>C000921884 - CHAUPIN HUAMANI GETRUDES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -21246,12 +21246,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001017337</t>
+          <t>C001141675</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C001017337 - TORRES MORALES DEOFELIA</t>
+          <t>C001141675 - RIVEROS BELLIDO JULIA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -21340,12 +21340,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C000920369</t>
+          <t>C001017337</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>C000920369 - DEZA SANDOVAL FRIDA MARILU</t>
+          <t>C001017337 - TORRES MORALES DEOFELIA</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S225" t="inlineStr"/>
@@ -21434,12 +21434,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C000921710</t>
+          <t>C001336201</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>C000921710 - PAREDES ROCA DARIO OCTAVIO</t>
+          <t>C001336201 - CURI VALENCIA ANTONIA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -21491,12 +21491,12 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21528,12 +21528,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C000921884</t>
+          <t>C004169742</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C000921884 - CHAUPIN HUAMANI GETRUDES</t>
+          <t>C004169742 - QUISPE SOSA MARILYN CYNTHIA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -21622,12 +21622,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C004169742</t>
+          <t>C001637483</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C004169742 - QUISPE SOSA MARILYN CYNTHIA</t>
+          <t>C001637483 - ORE GARCIA WALDO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S228" t="inlineStr"/>
@@ -21900,12 +21900,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C001637483</t>
+          <t>C001216332</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001637483 - ORE GARCIA WALDO</t>
+          <t>C001216332 - GARCIA GARCIA DE ORE LAURA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -21936,7 +21936,7 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S231" t="inlineStr"/>
@@ -22464,12 +22464,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004167253</t>
+          <t>C001745080</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C004167253 - PAREJA MENDOZA ALEJANDRA</t>
+          <t>C001745080 - CRUZATT ARROYO ELIZABETH</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -22521,12 +22521,12 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22558,12 +22558,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C004174478</t>
+          <t>C001725257</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C004174478 - ZEA RONDINEL CHRISTIAN MANUEL</t>
+          <t>C001725257 - SULCA CANCHO HAYDEE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22604,23 +22604,19 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22652,12 +22648,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001745080</t>
+          <t>C001645681</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001745080 - CRUZATT ARROYO ELIZABETH</t>
+          <t>C001645681 - HUAMAN YUCRA MARIELA VIVIANA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -22698,7 +22694,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S239" t="inlineStr"/>
@@ -22709,12 +22705,12 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22746,12 +22742,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001645681</t>
+          <t>C004167253</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001645681 - HUAMAN YUCRA MARIELA VIVIANA</t>
+          <t>C004167253 - PAREJA MENDOZA ALEJANDRA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -22792,7 +22788,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S240" t="inlineStr"/>
@@ -22840,12 +22836,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C001725257</t>
+          <t>C004174478</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C001725257 - SULCA CANCHO HAYDEE</t>
+          <t>C004174478 - ZEA RONDINEL CHRISTIAN MANUEL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22886,19 +22882,23 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23118,12 +23118,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C001344284</t>
+          <t>C001459258</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C001344284 - MULTISERVICIOS SANEMI S.A.C.</t>
+          <t>C001459258 - OBREGON CERVANTES IRMA ZELMIRA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -23212,12 +23212,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001459258</t>
+          <t>C001344284</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C001459258 - OBREGON CERVANTES IRMA ZELMIRA</t>
+          <t>C001344284 - MULTISERVICIOS SANEMI S.A.C.</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -23588,12 +23588,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>C004054714</t>
+          <t>C004188406</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>C004054714 - NUÑEZ CONDE ISIDORA</t>
+          <t>C004188406 - CUBA PALOMINO CARMEN TERESA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23682,12 +23682,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>C004188406</t>
+          <t>C004188408</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>C004188406 - CUBA PALOMINO CARMEN TERESA</t>
+          <t>C004188408 - AYALA ISIDRO TEODORA IMELDA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -23776,12 +23776,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>C004188408</t>
+          <t>C004054714</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>C004188408 - AYALA ISIDRO TEODORA IMELDA</t>
+          <t>C004054714 - NUÑEZ CONDE ISIDORA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -23964,12 +23964,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C004218943</t>
+          <t>C004184768</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>C004218943 - VALDIFRAN S.A.C.</t>
+          <t>C004184768 - LLANTOY PARCO RUBIT MARINEZ</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -24058,12 +24058,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C004224109</t>
+          <t>C004185576</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>C004224109 - TABOADA POMAHUACRE CHARO VANESA</t>
+          <t>C004185576 - ZAMORA QUISPE MIRIAMS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S254" t="inlineStr"/>
@@ -24152,12 +24152,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C004184768</t>
+          <t>C004218943</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>C004184768 - LLANTOY PARCO RUBIT MARINEZ</t>
+          <t>C004218943 - VALDIFRAN S.A.C.</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -24246,12 +24246,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C004185576</t>
+          <t>C004224109</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>C004185576 - ZAMORA QUISPE MIRIAMS</t>
+          <t>C004224109 - TABOADA POMAHUACRE CHARO VANESA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S256" t="inlineStr"/>
@@ -24340,12 +24340,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C001753798</t>
+          <t>C004051583</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>C001753798 - TACAS QUISPE YOVANA</t>
+          <t>C004051583 - IRCANAUPA CONGA JAIME MAMERTO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S257" t="inlineStr"/>
@@ -24434,12 +24434,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C001501700</t>
+          <t>C004051585</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>C001501700 - MITMA HUARCAYA YUDITH ROCIO</t>
+          <t>C004051585 - HUAMANI VILCHEZ ERNESTINA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24486,13 +24486,17 @@
       <c r="S258" t="inlineStr"/>
       <c r="T258" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24524,12 +24528,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001761104</t>
+          <t>C004036831</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C001761104 - AVENDANO CACERES LIZ JUDYTH</t>
+          <t>C004036831 - RIVERA AYALA HENY GIOVANA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -24570,7 +24574,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S259" t="inlineStr"/>
@@ -24618,12 +24622,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C001763348</t>
+          <t>C001761104</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>C001763348 - PALOMINO ARONES FREDY</t>
+          <t>C001761104 - AVENDANO CACERES LIZ JUDYTH</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -24675,12 +24679,12 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24716,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C001763579</t>
+          <t>C001763348</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C001763579 - VILCHEZ HUAMANI IRIS MARLENY</t>
+          <t>C001763348 - PALOMINO ARONES FREDY</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -24769,12 +24773,12 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -24806,12 +24810,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C004036831</t>
+          <t>C001763579</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>C004036831 - RIVERA AYALA HENY GIOVANA</t>
+          <t>C001763579 - VILCHEZ HUAMANI IRIS MARLENY</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24852,7 +24856,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S262" t="inlineStr"/>
@@ -24900,12 +24904,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C004051583</t>
+          <t>C001753798</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>C004051583 - IRCANAUPA CONGA JAIME MAMERTO</t>
+          <t>C001753798 - TACAS QUISPE YOVANA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -24946,7 +24950,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S263" t="inlineStr"/>
@@ -24994,12 +24998,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C004051585</t>
+          <t>C001155651</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C004051585 - HUAMANI VILCHEZ ERNESTINA</t>
+          <t>C001155651 - BAUTISTA GUTIERREZ LYDIA ELIZABETH</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -25088,12 +25092,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C001155651</t>
+          <t>C001501700</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C001155651 - BAUTISTA GUTIERREZ LYDIA ELIZABETH</t>
+          <t>C001501700 - MITMA HUARCAYA YUDITH ROCIO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -25140,17 +25144,13 @@
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr"/>
       <c r="V265" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25182,12 +25182,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C004197260</t>
+          <t>C004188397</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C004197260 - PALOMINO PARIONA RUTH</t>
+          <t>C004188397 - TENORIO CABRERA CLEOFE</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S266" t="inlineStr"/>
@@ -25276,12 +25276,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C004188397</t>
+          <t>C004197260</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C004188397 - TENORIO CABRERA CLEOFE</t>
+          <t>C004197260 - PALOMINO PARIONA RUTH</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S267" t="inlineStr"/>
@@ -25464,12 +25464,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C001672279</t>
+          <t>C001216674</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C001672279 - CONDE QUISPE VICENTA</t>
+          <t>C001216674 - CHUCHON DE HUAMANI CELEDONIA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S269" t="inlineStr"/>
@@ -25558,12 +25558,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001743417</t>
+          <t>C001383840</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>C001743417 - CRUZ QUISPE MARLENY</t>
+          <t>C001383840 - LAPA HUICHO LIDUBINA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S270" t="inlineStr"/>
@@ -25652,12 +25652,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001723404</t>
+          <t>C001225339</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>C001723404 - DE LA CRUZ QUISPE ROCIO</t>
+          <t>C001225339 - MENESES YANCE HERLINDA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -25746,12 +25746,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C001728928</t>
+          <t>C001446913</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C001728928 - GALINDO PIZARRO NORMA ISABEL</t>
+          <t>C001446913 - CASTRO MARTINEZ MARISOL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -25803,12 +25803,12 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25840,12 +25840,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001730719</t>
+          <t>C001543323</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001730719 - PEREZ DE LA CRUZ ANA</t>
+          <t>C001543323 - LAHUANA PRADO FLORECINDA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25934,12 +25934,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001225339</t>
+          <t>C001566424</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C001225339 - MENESES YANCE HERLINDA</t>
+          <t>C001566424 - JERI SOLIER ENMA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -26028,12 +26028,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001216674</t>
+          <t>C001569167</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C001216674 - CHUCHON DE HUAMANI CELEDONIA</t>
+          <t>C001569167 - BAUTISTA SALVATIERRA VICTOR</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S275" t="inlineStr"/>
@@ -26122,12 +26122,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C001383840</t>
+          <t>C001672279</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>C001383840 - LAPA HUICHO LIDUBINA</t>
+          <t>C001672279 - CONDE QUISPE VICENTA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -26216,12 +26216,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C001543323</t>
+          <t>C001728928</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C001543323 - LAHUANA PRADO FLORECINDA</t>
+          <t>C001728928 - GALINDO PIZARRO NORMA ISABEL</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -26273,12 +26273,12 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26310,12 +26310,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>C001566424</t>
+          <t>C001730719</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>C001566424 - JERI SOLIER ENMA</t>
+          <t>C001730719 - PEREZ DE LA CRUZ ANA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -26404,12 +26404,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C001569167</t>
+          <t>C001723404</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C001569167 - BAUTISTA SALVATIERRA VICTOR</t>
+          <t>C001723404 - DE LA CRUZ QUISPE ROCIO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -26498,12 +26498,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C001446913</t>
+          <t>C001743417</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C001446913 - CASTRO MARTINEZ MARISOL</t>
+          <t>C001743417 - CRUZ QUISPE MARLENY</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S280" t="inlineStr"/>
@@ -26780,12 +26780,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001582952</t>
+          <t>C001173371</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001582952 - DELGADO MUCHA ROSA</t>
+          <t>C001173371 - FLORES MITACC VICTOR</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S283" t="inlineStr"/>
@@ -26874,12 +26874,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C001626164</t>
+          <t>C001582952</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C001626164 - COLLAHUACHO GUTIERREZ LUCIA</t>
+          <t>C001582952 - DELGADO MUCHA ROSA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -26968,12 +26968,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C001173371</t>
+          <t>C001626164</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>C001173371 - FLORES MITACC VICTOR</t>
+          <t>C001626164 - COLLAHUACHO GUTIERREZ LUCIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -27014,7 +27014,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S285" t="inlineStr"/>
@@ -27152,12 +27152,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001739552</t>
+          <t>C001749414</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C001739552 - HUAMAN ZARATE NELY MARILUZ</t>
+          <t>C001749414 - CISNEROS PRADO LEYLA MERCEDES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -27246,12 +27246,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C001749414</t>
+          <t>C001739552</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C001749414 - CISNEROS PRADO LEYLA MERCEDES</t>
+          <t>C001739552 - HUAMAN ZARATE NELY MARILUZ</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -27524,12 +27524,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C001753432</t>
+          <t>C000920733</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C001753432 - BARBOZA VELASQUEZ NOLBERTA</t>
+          <t>C000920733 - FLORES PAUCCA PAULINA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -27570,7 +27570,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S291" t="inlineStr"/>
@@ -27618,12 +27618,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001766752</t>
+          <t>C000920683</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C001766752 - YARANGA CONTRERAS YANINA YANETT</t>
+          <t>C000920683 - LAURA LLANTOY FILOMENA LEONORA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -27712,12 +27712,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C004161363</t>
+          <t>C001766752</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>C004161363 - CEDANO QUISPE PAULINA</t>
+          <t>C001766752 - YARANGA CONTRERAS YANINA YANETT</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -27758,7 +27758,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S293" t="inlineStr"/>
@@ -27806,12 +27806,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C004183670</t>
+          <t>C004161363</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>C004183670 - VILLFIG INVERSIONES S.A.C.</t>
+          <t>C004161363 - CEDANO QUISPE PAULINA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S294" t="inlineStr"/>
@@ -27863,12 +27863,12 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27900,12 +27900,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C004187499</t>
+          <t>C004183670</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>C004187499 - AYALA LUQUE JENNIFER</t>
+          <t>C004183670 - VILLFIG INVERSIONES S.A.C.</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S295" t="inlineStr"/>
@@ -27957,12 +27957,12 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27994,12 +27994,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C001727645</t>
+          <t>C004187499</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C001727645 - ROJAS RODRIGUEZ ROSALI ROXANA</t>
+          <t>C004187499 - AYALA LUQUE JENNIFER</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -28040,19 +28040,23 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S296" t="inlineStr"/>
       <c r="T296" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28084,12 +28088,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C001667509</t>
+          <t>C001670779</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>C001667509 - QUISPE AUCCACUSI DELIA</t>
+          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -28130,7 +28134,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S297" t="inlineStr"/>
@@ -28178,12 +28182,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001659449</t>
+          <t>C001674831</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C001659449 - LOPEZ MACHACCA LOURDES FANNY</t>
+          <t>C001674831 - VILCHEZ JERI MAIRE PAMELA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -28224,7 +28228,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S298" t="inlineStr"/>
@@ -28272,12 +28276,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001670779</t>
+          <t>C001667509</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001670779 - QUICANO ALTAMIRANO ANA MARIA</t>
+          <t>C001667509 - QUISPE AUCCACUSI DELIA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -28318,7 +28322,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S299" t="inlineStr"/>
@@ -28366,12 +28370,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>C001674831</t>
+          <t>C001659449</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>C001674831 - VILCHEZ JERI MAIRE PAMELA</t>
+          <t>C001659449 - LOPEZ MACHACCA LOURDES FANNY</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -28412,7 +28416,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S300" t="inlineStr"/>
@@ -28460,12 +28464,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>C000920683</t>
+          <t>C001727645</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>C000920683 - LAURA LLANTOY FILOMENA LEONORA</t>
+          <t>C001727645 - ROJAS RODRIGUEZ ROSALI ROXANA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -28512,17 +28516,13 @@
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28554,12 +28554,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C000920318</t>
+          <t>C001753432</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C000920318 - YANQUI SALAS MARIA MARGARITA</t>
+          <t>C001753432 - BARBOZA VELASQUEZ NOLBERTA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -28648,12 +28648,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C000922061</t>
+          <t>C000922398</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>C000922061 - ROMERO RUIZ VILMA</t>
+          <t>C000922398 - REPRESENTACIONES KOYNOVORIN SRL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -28694,19 +28694,23 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S303" t="inlineStr"/>
       <c r="T303" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28738,12 +28742,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C000922029</t>
+          <t>C000922061</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>C000922029 - PANTOJA PANTOJA REBECA</t>
+          <t>C000922061 - ROMERO RUIZ VILMA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -28790,17 +28794,13 @@
       <c r="S304" t="inlineStr"/>
       <c r="T304" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28832,12 +28832,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C000920733</t>
+          <t>C000922029</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>C000920733 - FLORES PAUCCA PAULINA</t>
+          <t>C000922029 - PANTOJA PANTOJA REBECA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S305" t="inlineStr"/>
@@ -28926,12 +28926,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C000922398</t>
+          <t>C000920318</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>C000922398 - REPRESENTACIONES KOYNOVORIN SRL</t>
+          <t>C000920318 - YANQUI SALAS MARIA MARGARITA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S306" t="inlineStr"/>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -29020,17 +29020,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>C001155652</t>
+          <t>C001510464</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>C001155652 - NUNEZ GALINDO DELIA FLOR</t>
+          <t>C001510464 - CUYA CISNEROS VICTOR ANDRES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I307" s="2" t="n">
@@ -29043,7 +29043,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -29054,35 +29054,19 @@
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R307" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr"/>
       <c r="T307" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
       <c r="V307" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29104,7 +29088,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -29114,17 +29098,17 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>C001510464</t>
+          <t>C001413726</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>C001510464 - CUYA CISNEROS VICTOR ANDRES</t>
+          <t>C001413726 - FLORES GARCIA ELIZABETH ELVIRA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I308" s="2" t="n">
@@ -29137,7 +29121,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -29148,9 +29132,21 @@
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
-      <c r="R308" t="inlineStr"/>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
       <c r="S308" t="inlineStr"/>
       <c r="T308" t="inlineStr">
         <is>
@@ -29192,12 +29188,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001732349</t>
+          <t>C001487118</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>C001732349 - LUJAN LIMACO ESTELA</t>
+          <t>C001487118 - OSNAYO GUILLEN MARIANO CEBRIAN</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -29238,7 +29234,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S309" t="inlineStr"/>
@@ -29380,12 +29376,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C001487118</t>
+          <t>C001732349</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C001487118 - OSNAYO GUILLEN MARIANO CEBRIAN</t>
+          <t>C001732349 - LUJAN LIMACO ESTELA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -29426,7 +29422,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S311" t="inlineStr"/>
@@ -29474,12 +29470,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C001413726</t>
+          <t>C001155652</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C001413726 - FLORES GARCIA ELIZABETH ELVIRA</t>
+          <t>C001155652 - NUNEZ GALINDO DELIA FLOR</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -29526,13 +29522,17 @@
       <c r="S312" t="inlineStr"/>
       <c r="T312" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U312" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V312" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29658,12 +29658,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>C001711513</t>
+          <t>C004182546</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
+          <t>C004182546 - PRADO ROCA EDITH</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -29704,7 +29704,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S314" t="inlineStr"/>
@@ -29752,12 +29752,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C001687768</t>
+          <t>C004188982</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
+          <t>C004188982 - FERNANDEZ VILLANUEVA NERY</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -29809,12 +29809,12 @@
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29846,12 +29846,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C004182546</t>
+          <t>C004189005</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C004182546 - PRADO ROCA EDITH</t>
+          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -29898,17 +29898,13 @@
       <c r="S316" t="inlineStr"/>
       <c r="T316" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr"/>
       <c r="V316" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29940,12 +29936,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C004188982</t>
+          <t>C001687768</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>C004188982 - FERNANDEZ VILLANUEVA NERY</t>
+          <t>C001687768 - URBINA FLORES MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -29997,12 +29993,12 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30034,12 +30030,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>C004189005</t>
+          <t>C001711513</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>C004189005 - TAIPE CRUZ ELIZABETH</t>
+          <t>C001711513 - MENESES LUYO KELLY EVANS</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -30080,19 +30076,23 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S318" t="inlineStr"/>
       <c r="T318" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30218,12 +30218,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C001731479</t>
+          <t>C001669740</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>C001731479 - LANDA QUISPE EDELBERTA</t>
+          <t>C001669740 - JANAMPA GALINDO FLORA</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -30312,12 +30312,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C001750377</t>
+          <t>C001669264</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>C001750377 - MULTISERVICIOS VIECAL S.A.C.</t>
+          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -30358,7 +30358,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S321" t="inlineStr"/>
@@ -30369,12 +30369,12 @@
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V321" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30406,12 +30406,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C001748093</t>
+          <t>C001731479</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
+          <t>C001731479 - LANDA QUISPE EDELBERTA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -30452,7 +30452,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S322" t="inlineStr"/>
@@ -30463,12 +30463,12 @@
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30500,12 +30500,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>C001584370</t>
+          <t>C001750377</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>C001584370 - ARESTEGUI CARRASCO MONICA GLADYS</t>
+          <t>C001750377 - MULTISERVICIOS VIECAL S.A.C.</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -30546,19 +30546,23 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S323" t="inlineStr"/>
       <c r="T323" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30590,12 +30594,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>C001668200</t>
+          <t>C001748093</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
+          <t>C001748093 - LLAMOCCA QUISPE JUAN</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -30636,7 +30640,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S324" t="inlineStr"/>
@@ -30684,12 +30688,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>C001663297</t>
+          <t>C001473641</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>C001663297 - SUAREZ ATAUQUI ZENAIDA</t>
+          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -30778,12 +30782,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C001669740</t>
+          <t>C001491694</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>C001669740 - JANAMPA GALINDO FLORA</t>
+          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -30824,7 +30828,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -30835,12 +30839,12 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30872,12 +30876,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C001669264</t>
+          <t>C001584370</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C001669264 - DAVALOS PALOMINO EDGAR HERNAN</t>
+          <t>C001584370 - ARESTEGUI CARRASCO MONICA GLADYS</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -30918,23 +30922,19 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr"/>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -30966,12 +30966,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>C001491694</t>
+          <t>C001668200</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>C001491694 - SOTACURO MUÑOZ ALBINA</t>
+          <t>C001668200 - LLANTOY HUAMAN MIRIAM MARGOT</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S328" t="inlineStr"/>
@@ -31060,12 +31060,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>C001473641</t>
+          <t>C001663297</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>C001473641 - QUISPE JANAMPA YUDITH PAOLA</t>
+          <t>C001663297 - SUAREZ ATAUQUI ZENAIDA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -31154,12 +31154,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>C001217185</t>
+          <t>C000921781</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
+          <t>C000921781 - MENESES MENDIETA IRMA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -31211,12 +31211,12 @@
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31342,12 +31342,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>C000921781</t>
+          <t>C001217185</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>C000921781 - MENESES MENDIETA IRMA</t>
+          <t>C001217185 - HUARANCCA GARCIA OLGA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -31399,12 +31399,12 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
